--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00927-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00927-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94205D08-028A-48A6-862F-79E5B47842CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBB4C7E7-FE2D-4CF0-8743-070FDE5FB669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{942B096B-940F-42F9-9E9A-E15C4A8655D2}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{49C02A08-D663-4535-8495-945E9EF4F343}"/>
   </bookViews>
   <sheets>
     <sheet name="00927-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1534,20 +1534,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{543176EE-8757-44F2-B9B8-E39915958674}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{942C2604-2565-4D6A-88E2-9108CEA7A0B8}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1575,7 +1575,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1605,7 +1605,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1701,7 +1701,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1781,7 +1781,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>6.69</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>2.13</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="51" t="s">
         <v>49</v>
       </c>
